--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jherrerac\Desktop\BASE DE DATOS ELOY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF32B34C-8D54-48C2-A916-51B79DC22E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD101D8-CD63-4DE2-9635-A91EA149F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -5294,7 +5294,7 @@
         <v>46338</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4">
         <v>0</v>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jherrerac\Desktop\BASE DE DATOS ELOY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD101D8-CD63-4DE2-9635-A91EA149F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542D9131-EBCE-421C-8431-4FFF4985DBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -957,7 +957,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5287,14 +5288,12 @@
       <c r="A2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C2" s="5">
-        <v>46338</v>
-      </c>
+      <c r="B2" s="6">
+        <v>46092</v>
+      </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4">
         <v>0</v>
@@ -5325,8 +5324,8 @@
       <c r="A3" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="4">
         <v>0</v>
       </c>
@@ -5359,12 +5358,8 @@
       <c r="A4" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46254</v>
-      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="4">
         <v>3</v>
       </c>
@@ -5397,8 +5392,8 @@
       <c r="A5" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="4">
         <v>1</v>
       </c>
@@ -5431,10 +5426,8 @@
       <c r="A6" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="4">
         <v>3</v>
       </c>
@@ -5467,10 +5460,8 @@
       <c r="A7" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B7" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="4">
         <v>0</v>
       </c>
@@ -5503,10 +5494,8 @@
       <c r="A8" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="4">
         <v>0</v>
       </c>
@@ -5539,10 +5528,8 @@
       <c r="A9" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="4">
         <v>7</v>
       </c>
@@ -5575,10 +5562,8 @@
       <c r="A10" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B10" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="4">
         <v>3</v>
       </c>
@@ -5611,10 +5596,8 @@
       <c r="A11" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="5">
-        <v>46337</v>
-      </c>
-      <c r="C11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="4">
         <v>2</v>
       </c>
@@ -5647,8 +5630,8 @@
       <c r="A12" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="4">
         <v>5</v>
       </c>
@@ -5681,8 +5664,8 @@
       <c r="A13" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
       <c r="D13" s="4">
         <v>2</v>
       </c>
@@ -5715,8 +5698,8 @@
       <c r="A14" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="4">
         <v>0</v>
       </c>
@@ -5749,8 +5732,8 @@
       <c r="A15" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="4">
         <v>1</v>
       </c>
@@ -5783,8 +5766,8 @@
       <c r="A16" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="4">
         <v>0</v>
       </c>
@@ -5817,8 +5800,8 @@
       <c r="A17" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="4">
         <v>1</v>
       </c>
@@ -5851,8 +5834,8 @@
       <c r="A18" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="4">
         <v>0</v>
       </c>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jherrerac\Desktop\BASE DE DATOS ELOY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542D9131-EBCE-421C-8431-4FFF4985DBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250AC811-0B66-4F61-B33D-92791818641B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="277">
   <si>
     <t>Instrucciones</t>
   </si>
@@ -885,6 +885,9 @@
   </si>
   <si>
     <t>atributo</t>
+  </si>
+  <si>
+    <t>11-03-2026</t>
   </si>
 </sst>
 </file>
@@ -957,8 +960,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5237,7 +5240,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -5288,8 +5291,8 @@
       <c r="A2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="6">
-        <v>46092</v>
+      <c r="B2" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -5863,6 +5866,10 @@
       <c r="L18" s="4">
         <v>1</v>
       </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L18" xr:uid="{00000000-0009-0000-0000-000008000000}"/>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jherrerac\Desktop\BASE DE DATOS ELOY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250AC811-0B66-4F61-B33D-92791818641B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAA569B-5293-4EA6-944E-2E99066038DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -4803,10 +4803,10 @@
         <v>54</v>
       </c>
       <c r="C2" s="4">
-        <v>0.93</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D2" s="4">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>183</v>
@@ -4872,10 +4872,10 @@
         <v>54</v>
       </c>
       <c r="C5" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.95</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.98</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>189</v>
@@ -4895,10 +4895,10 @@
         <v>54</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>189</v>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jherrerac\Desktop\BASE DE DATOS ELOY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAA569B-5293-4EA6-944E-2E99066038DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D97357-CEA5-4222-939D-1E5DFC8C4B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -4803,7 +4803,7 @@
         <v>54</v>
       </c>
       <c r="C2" s="4">
-        <v>0.98499999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="D2" s="4">
         <v>0.95</v>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -22,9 +22,9 @@
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">LIMPIEZA_PRESUPUESTO!$A$1:$C$11</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">AULA911_CAMPUS!$A$1:$F$23</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">AULA911_TOP!$A$1:$B$6</definedName>
-    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">RONDAS!$A$1:$G$23</definedName>
+    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">RONDAS!$A$1:$H$23</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">PROYECTOS!$A$1:$G$20</definedName>
-    <definedName hidden="1" localSheetId="8" name="_xlnm._FilterDatabase">MEJORAS_PROGRAMACION!$A$1:$L$18</definedName>
+    <definedName hidden="1" localSheetId="8" name="_xlnm._FilterDatabase">MEJORAS_PROGRAMACION!$A$1:$N$18</definedName>
     <definedName hidden="1" localSheetId="9" name="_xlnm._FilterDatabase">MEJORAS_ESTADO!$A$1:$C$5</definedName>
     <definedName hidden="1" localSheetId="10" name="_xlnm._FilterDatabase">LISTO!$A$1:$G$19</definedName>
     <definedName hidden="1" localSheetId="11" name="_xlnm._FilterDatabase">CONFIG_HTML!$A$1:$D$1</definedName>
@@ -32,14 +32,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId16" roundtripDataChecksum="jnBgVXjyNwRPAHRFo44mZUnj6zmyTZLCZOXKpErk1kc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId16" roundtripDataChecksum="eXLbFrkQM9XP2+UauwaMpXzRouziBLINfamYXvmdepY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="280">
   <si>
     <t>Instrucciones</t>
   </si>
@@ -50,6 +50,9 @@
     <t>El HTML ya está programado para leer el archivo 'BD_dashboard_operaciones_github.xlsx' de forma automática al abrirse.</t>
   </si>
   <si>
+    <t>zona</t>
+  </si>
+  <si>
     <t>CÓMO USARLO:</t>
   </si>
   <si>
@@ -68,130 +71,133 @@
     <t>4. Al abrir o recargar el HTML, los datos se actualizan solos (no hay que tocar el código).</t>
   </si>
   <si>
+    <t>campus</t>
+  </si>
+  <si>
     <t>HOJAS Y SU FUNCIÓN:</t>
   </si>
   <si>
+    <t>indicador</t>
+  </si>
+  <si>
+    <t>dot_m</t>
+  </si>
+  <si>
     <t>KPIs_HTML: todas las tarjetas numéricas (KPI) del dashboard. Columnas: modulo, indicador, valor, unidad.</t>
   </si>
   <si>
-    <t>indicador</t>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>dot_t</t>
+  </si>
+  <si>
+    <t>unidad</t>
+  </si>
+  <si>
+    <t>dot_n</t>
+  </si>
+  <si>
+    <t>Limpieza</t>
+  </si>
+  <si>
+    <t>cob_m</t>
+  </si>
+  <si>
+    <t>cob_t</t>
+  </si>
+  <si>
+    <t>cob_n</t>
+  </si>
+  <si>
+    <t>pend_m</t>
+  </si>
+  <si>
+    <t>pend_t</t>
   </si>
   <si>
     <t xml:space="preserve">   unidad admite: porcentaje (valor como fracción, ej. 0.95 = 95%), entero, minutos, moneda, decimal.</t>
   </si>
   <si>
-    <t>valor</t>
+    <t>Cobertura semanal total</t>
+  </si>
+  <si>
+    <t>pend_n</t>
   </si>
   <si>
     <t>LIMPIEZA_COBERTURA: tabla de cobertura de limpieza por sede.</t>
   </si>
   <si>
-    <t>unidad</t>
+    <t>pend_total</t>
   </si>
   <si>
     <t>LIMPIEZA_PRESUPUESTO: montos mensuales de descuentos y penalidades. periodo en formato AAAA-MM.</t>
   </si>
   <si>
+    <t>cobertura_pct</t>
+  </si>
+  <si>
     <t>AULA911_CAMPUS: tiempos de atención y valoración por campus (Aula 911).</t>
   </si>
   <si>
-    <t>zona</t>
-  </si>
-  <si>
     <t>AULA911_TOP: participación (fracción 0-1) de los tipos de incidencia más frecuentes.</t>
   </si>
   <si>
-    <t>Limpieza</t>
-  </si>
-  <si>
     <t>RONDAS: cumplimiento de rondas por sede.</t>
   </si>
   <si>
-    <t>campus</t>
-  </si>
-  <si>
     <t>PROYECTOS: portafolio de proyectos 2026 (usado también en el detalle de Huánuco/Huamanga/Juliaca).</t>
   </si>
   <si>
-    <t>Cobertura semanal total</t>
-  </si>
-  <si>
-    <t>dot_m</t>
+    <t>LIMA</t>
   </si>
   <si>
     <t>MEJORAS_PROGRAMACION: iniciativas estratégicas por campus y mes.</t>
   </si>
   <si>
-    <t>dot_t</t>
-  </si>
-  <si>
     <t>porcentaje</t>
   </si>
   <si>
     <t>MEJORAS_ESTADO: conteo de iniciativas por estado (Ejecutado/En proceso/Pendiente/Cancelado).</t>
   </si>
   <si>
-    <t>dot_n</t>
+    <t>SJL I</t>
   </si>
   <si>
     <t>Dotación programada (turnos)</t>
   </si>
   <si>
-    <t>cob_m</t>
-  </si>
-  <si>
     <t>LISTO: implementación del programa Listo por campus (incluye el detalle de Trujillo).</t>
   </si>
   <si>
     <t>entero</t>
   </si>
   <si>
-    <t>cob_t</t>
-  </si>
-  <si>
     <t>CONFIG_HTML (opcional): permite sobrescribir textos puntuales del HTML por selector CSS.</t>
   </si>
   <si>
-    <t>cob_n</t>
-  </si>
-  <si>
     <t>Turnos cubiertos</t>
   </si>
   <si>
-    <t>pend_m</t>
-  </si>
-  <si>
     <t xml:space="preserve">   selector 'meta:&lt;id-seccion&gt;:eyebrow' o 'meta:&lt;id-seccion&gt;:title' cambia los títulos de cada sección.</t>
   </si>
   <si>
-    <t>pend_t</t>
-  </si>
-  <si>
     <t>Turnos pendientes</t>
   </si>
   <si>
-    <t>pend_n</t>
-  </si>
-  <si>
-    <t>pend_total</t>
-  </si>
-  <si>
     <t>Presupuesto 2026</t>
   </si>
   <si>
-    <t>cobertura_pct</t>
-  </si>
-  <si>
     <t>moneda</t>
   </si>
   <si>
     <t>Presupuesto ejecutado</t>
   </si>
   <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>SJL I</t>
+    <t>ALMACEN CENTRAL</t>
+  </si>
+  <si>
+    <t>periodo</t>
   </si>
   <si>
     <t>Nivel de ejecución</t>
@@ -206,16 +212,16 @@
     <t># incidencias</t>
   </si>
   <si>
-    <t>ALMACEN CENTRAL</t>
-  </si>
-  <si>
     <t>Tiempo acepta solicitud</t>
   </si>
   <si>
+    <t>minutos</t>
+  </si>
+  <si>
     <t>JARRITA</t>
   </si>
   <si>
-    <t>minutos</t>
+    <t>concepto</t>
   </si>
   <si>
     <t>Tiempo atiende solicitud</t>
@@ -224,108 +230,102 @@
     <t>Tiempo total de atención</t>
   </si>
   <si>
+    <t>monto</t>
+  </si>
+  <si>
+    <t>Valoración general</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>Rondas</t>
+  </si>
+  <si>
+    <t>% cumplimiento</t>
+  </si>
+  <si>
+    <t>Descuentos faltas/tardanzas</t>
+  </si>
+  <si>
+    <t>% cumplimiento encargado</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
     <t>TORRE NUEVA</t>
   </si>
   <si>
-    <t>Valoración general</t>
-  </si>
-  <si>
-    <t>decimal</t>
-  </si>
-  <si>
-    <t>Rondas</t>
-  </si>
-  <si>
-    <t>% cumplimiento</t>
-  </si>
-  <si>
-    <t>% cumplimiento encargado</t>
+    <t>% cumplimiento Asistente</t>
+  </si>
+  <si>
+    <t>2026-07</t>
   </si>
   <si>
     <t>LIMA NORTE</t>
   </si>
   <si>
-    <t>% cumplimiento Asistente</t>
-  </si>
-  <si>
-    <t>periodo</t>
+    <t>Total programado</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>Total ejecutado</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t># checkpoints</t>
+  </si>
+  <si>
+    <t>Proyectos</t>
+  </si>
+  <si>
+    <t>Penalidades</t>
   </si>
   <si>
     <t>PROVINCIA</t>
   </si>
   <si>
-    <t>Total programado</t>
+    <t>En proceso</t>
   </si>
   <si>
     <t>AREQUIPA POSTGRADO</t>
   </si>
   <si>
-    <t>Total ejecutado</t>
-  </si>
-  <si>
-    <t>concepto</t>
-  </si>
-  <si>
-    <t>monto</t>
-  </si>
-  <si>
-    <t># checkpoints</t>
+    <t>Pendientes</t>
+  </si>
+  <si>
+    <t>Listo</t>
+  </si>
+  <si>
+    <t>Registros</t>
+  </si>
+  <si>
+    <t>Operativos</t>
+  </si>
+  <si>
+    <t>Por implementar</t>
   </si>
   <si>
     <t>CHIMBOTE</t>
   </si>
   <si>
-    <t>Proyectos</t>
-  </si>
-  <si>
-    <t>2026-05</t>
-  </si>
-  <si>
-    <t>Descuentos faltas/tardanzas</t>
-  </si>
-  <si>
-    <t>En proceso</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
     <t>PIURA</t>
   </si>
   <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>Pendientes</t>
-  </si>
-  <si>
-    <t>Listo</t>
-  </si>
-  <si>
-    <t>Penalidades</t>
-  </si>
-  <si>
-    <t>Registros</t>
-  </si>
-  <si>
     <t>HUANCAYO</t>
   </si>
   <si>
-    <t>Operativos</t>
-  </si>
-  <si>
-    <t>Por implementar</t>
-  </si>
-  <si>
     <t>HUANUCO</t>
   </si>
   <si>
@@ -362,6 +362,24 @@
     <t>OFICINAS ADMINISTRATIVA</t>
   </si>
   <si>
+    <t>AREQUIPA I</t>
+  </si>
+  <si>
+    <t>SJL II</t>
+  </si>
+  <si>
+    <t>AREQUIPA III</t>
+  </si>
+  <si>
+    <t>AREQUIPA II</t>
+  </si>
+  <si>
+    <t>EPG SALAVERRY</t>
+  </si>
+  <si>
+    <t>JOSE DIAZ</t>
+  </si>
+  <si>
     <t>tiempo_acepta_min</t>
   </si>
   <si>
@@ -371,9 +389,6 @@
     <t>tiempo_total_min</t>
   </si>
   <si>
-    <t>AREQUIPA I</t>
-  </si>
-  <si>
     <t>valoracion</t>
   </si>
   <si>
@@ -383,36 +398,21 @@
     <t>CAMPUS CHIMBOTE</t>
   </si>
   <si>
-    <t>SJL II</t>
-  </si>
-  <si>
-    <t>AREQUIPA III</t>
-  </si>
-  <si>
     <t>CAMPUS TRUJILLO</t>
   </si>
   <si>
-    <t>AREQUIPA II</t>
-  </si>
-  <si>
     <t>CAMPUS PIURA</t>
   </si>
   <si>
     <t>CAMPUS AREQUIPA</t>
   </si>
   <si>
-    <t>EPG SALAVERRY</t>
-  </si>
-  <si>
     <t>Tacna y Arica</t>
   </si>
   <si>
     <t>Parra</t>
   </si>
   <si>
-    <t>JOSE DIAZ</t>
-  </si>
-  <si>
     <t>Parra 2</t>
   </si>
   <si>
@@ -446,42 +446,42 @@
     <t>Sede Central</t>
   </si>
   <si>
+    <t>tipo_incidencia</t>
+  </si>
+  <si>
     <t>CAMPUS ICA</t>
   </si>
   <si>
+    <t>participacion</t>
+  </si>
+  <si>
     <t>CAMPUS TACNA</t>
   </si>
   <si>
+    <t>Problema con la PC</t>
+  </si>
+  <si>
+    <t>Problema con el proyector</t>
+  </si>
+  <si>
     <t>CAMPUS PUCALLPA</t>
   </si>
   <si>
+    <t>Ambiente cerrado</t>
+  </si>
+  <si>
     <t>CAMPUS LIMA NORTE UTP</t>
   </si>
   <si>
+    <t>Problema con el audio</t>
+  </si>
+  <si>
+    <t>Problema con el Zoom</t>
+  </si>
+  <si>
     <t>CAMPUS LIMA SUR UTP</t>
   </si>
   <si>
-    <t>tipo_incidencia</t>
-  </si>
-  <si>
-    <t>participacion</t>
-  </si>
-  <si>
-    <t>Problema con la PC</t>
-  </si>
-  <si>
-    <t>Problema con el proyector</t>
-  </si>
-  <si>
-    <t>Ambiente cerrado</t>
-  </si>
-  <si>
-    <t>Problema con el audio</t>
-  </si>
-  <si>
-    <t>Problema con el Zoom</t>
-  </si>
-  <si>
     <t>sede</t>
   </si>
   <si>
@@ -500,99 +500,99 @@
     <t>cumplimiento_pct</t>
   </si>
   <si>
+    <t>04. UTP Ate</t>
+  </si>
+  <si>
+    <t>03. UTP SJL</t>
+  </si>
+  <si>
+    <t>11. UTP Huancayo</t>
+  </si>
+  <si>
+    <t>07. UTP Chiclayo</t>
+  </si>
+  <si>
+    <t>05. UTP Lima Sur</t>
+  </si>
+  <si>
+    <t>06. UTP Arequipa</t>
+  </si>
+  <si>
+    <t>02. UTP Arequipa Parra I</t>
+  </si>
+  <si>
+    <t>03. UTP Arequipa Parra II</t>
+  </si>
+  <si>
     <t>01. UTP Arequipa Tacna y Arica</t>
   </si>
   <si>
+    <t>09. UTP Piura</t>
+  </si>
+  <si>
     <t>01. UTP Lima Centro</t>
   </si>
   <si>
+    <t>03. UTP Lima Centro Torre Petit Thouars</t>
+  </si>
+  <si>
     <t>01. UTP Lima Centro Sede Central</t>
   </si>
   <si>
-    <t>02. UTP Arequipa Parra I</t>
+    <t>04. UTP Lima Centro Torre Pacifico</t>
   </si>
   <si>
     <t>02. UTP Lima Centro Torre Arequipa</t>
   </si>
   <si>
+    <t>13. UTP Iquitos</t>
+  </si>
+  <si>
+    <t>proyecto</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>14. UTP Pucallpa</t>
+  </si>
+  <si>
+    <t>avance_obra_pct</t>
+  </si>
+  <si>
+    <t>avance_compras_pct</t>
+  </si>
+  <si>
+    <t>avance_implementación_pct</t>
+  </si>
+  <si>
+    <t>fecha_objetivo_texto</t>
+  </si>
+  <si>
     <t>02. UTP Lima Norte</t>
   </si>
   <si>
-    <t>03. UTP Arequipa Parra II</t>
-  </si>
-  <si>
-    <t>03. UTP Lima Centro Torre Petit Thouars</t>
-  </si>
-  <si>
-    <t>03. UTP SJL</t>
-  </si>
-  <si>
-    <t>04. UTP Ate</t>
-  </si>
-  <si>
-    <t>04. UTP Lima Centro Torre Pacifico</t>
-  </si>
-  <si>
-    <t>05. UTP Lima Sur</t>
-  </si>
-  <si>
-    <t>06. UTP Arequipa</t>
-  </si>
-  <si>
-    <t>07. UTP Chiclayo</t>
+    <t>con_observaciones</t>
+  </si>
+  <si>
+    <t>nueva_fecha_texto</t>
+  </si>
+  <si>
+    <t>Nuevo Edificio Campus Lima Norte (Salud) – Por definir ITSE</t>
+  </si>
+  <si>
+    <t>12. UTP Trujillo</t>
   </si>
   <si>
     <t>08. UTP Ica</t>
   </si>
   <si>
-    <t>09. UTP Piura</t>
-  </si>
-  <si>
     <t>10. UTP Chimbote</t>
   </si>
   <si>
-    <t>11. UTP Huancayo</t>
-  </si>
-  <si>
-    <t>12. UTP Trujillo</t>
-  </si>
-  <si>
-    <t>13. UTP Iquitos</t>
-  </si>
-  <si>
-    <t>14. UTP Pucallpa</t>
-  </si>
-  <si>
     <t>15. UTP Tacna</t>
   </si>
   <si>
-    <t>proyecto</t>
-  </si>
-  <si>
-    <t>estado</t>
-  </si>
-  <si>
-    <t>avance_obra_pct</t>
-  </si>
-  <si>
-    <t>avance_compras_pct</t>
-  </si>
-  <si>
-    <t>avance_implementación_pct</t>
-  </si>
-  <si>
-    <t>fecha_objetivo_texto</t>
-  </si>
-  <si>
-    <t>con_observaciones</t>
-  </si>
-  <si>
-    <t>nueva_fecha_texto</t>
-  </si>
-  <si>
-    <t>Nuevo Edificio Campus Lima Norte (Salud) – Por definir ITSE</t>
-  </si>
-  <si>
     <t>SET 26</t>
   </si>
   <si>
@@ -626,31 +626,49 @@
     <t>fecha_fin_texto</t>
   </si>
   <si>
+    <t>Nuevo Campus Juliaca – ITSE - 18/11</t>
+  </si>
+  <si>
     <t>mar</t>
   </si>
   <si>
-    <t>Nuevo Campus Juliaca – ITSE - 18/11</t>
-  </si>
-  <si>
     <t>abr</t>
   </si>
   <si>
+    <t>NOV 26</t>
+  </si>
+  <si>
     <t>may</t>
   </si>
   <si>
+    <t>Nuevos Laboratorios de Hotelería y Turismo – Lima Centro</t>
+  </si>
+  <si>
     <t>jun</t>
   </si>
   <si>
-    <t>NOV 26</t>
-  </si>
-  <si>
-    <t>ago</t>
+    <t>jul</t>
+  </si>
+  <si>
+    <t>ENE 27</t>
+  </si>
+  <si>
+    <t>Nuevos Laboratorios de Odontología – Lima Centro - Jarrita</t>
+  </si>
+  <si>
+    <t>MAR 27</t>
+  </si>
+  <si>
+    <t>agos</t>
   </si>
   <si>
     <t>set</t>
   </si>
   <si>
-    <t>Nuevos Laboratorios de Hotelería y Turismo – Lima Centro</t>
+    <t>Nuevo Campus Cusco</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
   </si>
   <si>
     <t>oct</t>
@@ -659,99 +677,87 @@
     <t>nov</t>
   </si>
   <si>
+    <t>cantidad</t>
+  </si>
+  <si>
+    <t>JUL 27</t>
+  </si>
+  <si>
+    <t>dic</t>
+  </si>
+  <si>
     <t>total</t>
   </si>
   <si>
-    <t>ENE 27</t>
+    <t>Ampliación Campus Huancayo</t>
+  </si>
+  <si>
+    <t>Ejecutado</t>
   </si>
   <si>
     <t>Corporativo - Natalio</t>
   </si>
   <si>
-    <t>Nuevos Laboratorios de Odontología – Lima Centro - Jarrita</t>
-  </si>
-  <si>
-    <t>MAR 27</t>
-  </si>
-  <si>
-    <t>Nuevo Campus Cusco</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>JUL 27</t>
-  </si>
-  <si>
-    <t>Ampliación Campus Huancayo</t>
-  </si>
-  <si>
     <t>AGO 27</t>
   </si>
   <si>
+    <t>Ampliación Campus Piura</t>
+  </si>
+  <si>
+    <t>Remodelación de Saco Oliveros</t>
+  </si>
+  <si>
     <t>UTP Arequipa</t>
   </si>
   <si>
-    <t>Ampliación Campus Piura</t>
-  </si>
-  <si>
-    <t>Remodelación de Saco Oliveros</t>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Clínica Odontológica – Guzman Blanco</t>
   </si>
   <si>
     <t>UTP Chiclayo</t>
   </si>
   <si>
-    <t>Clínica Odontológica – Guzman Blanco</t>
+    <t>Idat Campus SJL</t>
   </si>
   <si>
     <t>UTP Chimbote</t>
   </si>
   <si>
-    <t>Idat Campus SJL</t>
+    <t>Idat Campus SJM</t>
   </si>
   <si>
     <t>UTP Huancayo</t>
   </si>
   <si>
-    <t>Idat Campus SJM</t>
+    <t>Idat Chiclayo</t>
   </si>
   <si>
     <t>UTP Ica</t>
   </si>
   <si>
-    <t>Idat Chiclayo</t>
-  </si>
-  <si>
     <t>Medicina Ica</t>
   </si>
   <si>
+    <t>Medicina Trujillo</t>
+  </si>
+  <si>
     <t>UTP Iquitos</t>
   </si>
   <si>
-    <t>Medicina Trujillo</t>
+    <t>Medicina Piura</t>
   </si>
   <si>
     <t>UTP Lima Centro</t>
   </si>
   <si>
-    <t>cantidad</t>
-  </si>
-  <si>
-    <t>Medicina Piura</t>
-  </si>
-  <si>
     <t>UTP Lima Este</t>
   </si>
   <si>
-    <t>Ejecutado</t>
-  </si>
-  <si>
     <t>UTP Lima Norte</t>
   </si>
   <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
     <t>UTP Lima Sur</t>
   </si>
   <si>
@@ -776,12 +782,21 @@
     <t>diseno_pct</t>
   </si>
   <si>
+    <t>selector</t>
+  </si>
+  <si>
     <t>obra_pct</t>
   </si>
   <si>
+    <t>tipo</t>
+  </si>
+  <si>
     <t>operacion</t>
   </si>
   <si>
+    <t>atributo</t>
+  </si>
+  <si>
     <t>con_observacion</t>
   </si>
   <si>
@@ -864,15 +879,6 @@
   </si>
   <si>
     <t>Resto de campus (IV)</t>
-  </si>
-  <si>
-    <t>selector</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>atributo</t>
   </si>
 </sst>
 </file>
@@ -940,7 +946,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -959,8 +965,14 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1249,27 +1261,27 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
@@ -1277,72 +1289,72 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1"/>
@@ -2344,18 +2356,18 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B2" s="4">
         <v>80.0</v>
@@ -2366,7 +2378,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4">
         <v>111.0</v>
@@ -2377,7 +2389,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4" s="4">
         <v>76.0</v>
@@ -2388,7 +2400,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B5" s="4">
         <v>27.0</v>
@@ -3420,30 +3432,30 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B2" s="4">
         <v>1.0</v>
@@ -3452,13 +3464,13 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>185</v>
@@ -3466,7 +3478,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B3" s="4">
         <v>1.0</v>
@@ -3475,21 +3487,21 @@
         <v>1.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B4" s="4">
         <v>1.0</v>
@@ -3498,13 +3510,13 @@
         <v>1.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>185</v>
@@ -3512,7 +3524,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B5" s="4">
         <v>1.0</v>
@@ -3521,13 +3533,13 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>185</v>
@@ -3535,7 +3547,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B6" s="4">
         <v>1.0</v>
@@ -3544,13 +3556,13 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>185</v>
@@ -3558,7 +3570,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B7" s="4">
         <v>1.0</v>
@@ -3567,13 +3579,13 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>185</v>
@@ -3581,7 +3593,7 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B8" s="4">
         <v>1.0</v>
@@ -3590,13 +3602,13 @@
         <v>1.0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>185</v>
@@ -3604,7 +3616,7 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B9" s="4">
         <v>1.0</v>
@@ -3613,21 +3625,21 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B10" s="4">
         <v>1.0</v>
@@ -3636,21 +3648,21 @@
         <v>1.0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B11" s="4">
         <v>1.0</v>
@@ -3659,21 +3671,21 @@
         <v>1.0</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B12" s="4">
         <v>1.0</v>
@@ -3682,13 +3694,13 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>185</v>
@@ -3696,7 +3708,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B13" s="4">
         <v>1.0</v>
@@ -3719,7 +3731,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B14" s="4">
         <v>1.0</v>
@@ -3731,7 +3743,7 @@
         <v>185</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>185</v>
@@ -3742,7 +3754,7 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B15" s="4">
         <v>1.0</v>
@@ -3754,14 +3766,14 @@
         <v>185</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B16" s="4">
         <v>0.8</v>
@@ -3773,7 +3785,7 @@
         <v>185</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>185</v>
@@ -3784,7 +3796,7 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B17" s="4">
         <v>0.8</v>
@@ -3796,7 +3808,7 @@
         <v>185</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>185</v>
@@ -3807,7 +3819,7 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B18" s="4">
         <v>0.8</v>
@@ -3819,7 +3831,7 @@
         <v>185</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>185</v>
@@ -3830,7 +3842,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B19" s="4">
         <v>0.0</v>
@@ -4857,16 +4869,16 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1"/>
@@ -5893,150 +5905,150 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="4">
         <v>0.95</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4">
         <v>616.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4">
         <v>584.0</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C5" s="4">
         <v>32.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" s="4">
         <v>1.8E7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4">
         <v>1.12E7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4">
         <v>0.622</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" s="4">
         <v>222439.0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4">
         <v>21040.0</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4">
         <v>4.7</v>
@@ -6047,10 +6059,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" s="4">
         <v>4.7</v>
@@ -6061,10 +6073,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4">
         <v>9.4</v>
@@ -6075,184 +6087,184 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" s="4">
         <v>4.6</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15" s="4">
         <v>0.71</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C16" s="4">
         <v>0.57</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C17" s="4">
         <v>0.77</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C18" s="4">
         <v>106191.0</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C19" s="4">
         <v>97422.0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C20" s="4">
         <v>678.0</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" s="4">
         <v>19.0</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22" s="4">
         <v>8.0</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C23" s="4">
         <v>11.0</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4">
         <v>18.0</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="C25" s="4">
         <v>11.0</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C26" s="4">
         <v>7.0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1"/>
@@ -7255,51 +7267,51 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C2" s="4">
         <v>9.0</v>
@@ -7337,10 +7349,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C3" s="4">
         <v>1.0</v>
@@ -7378,10 +7390,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4">
         <v>3.0</v>
@@ -7419,10 +7431,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4">
         <v>15.0</v>
@@ -7460,10 +7472,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4">
         <v>19.0</v>
@@ -7501,10 +7513,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4">
         <v>1.0</v>
@@ -7542,10 +7554,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4">
         <v>16.0</v>
@@ -7583,10 +7595,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4">
         <v>15.0</v>
@@ -7624,10 +7636,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C10" s="4">
         <v>8.0</v>
@@ -7665,10 +7677,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4">
         <v>13.0</v>
@@ -7706,7 +7718,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>95</v>
@@ -7747,7 +7759,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>96</v>
@@ -7788,7 +7800,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>97</v>
@@ -7829,7 +7841,7 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>98</v>
@@ -7870,7 +7882,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>99</v>
@@ -7911,7 +7923,7 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>100</v>
@@ -7952,7 +7964,7 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>101</v>
@@ -7993,7 +8005,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>102</v>
@@ -8034,7 +8046,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>103</v>
@@ -8075,7 +8087,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>104</v>
@@ -8116,7 +8128,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>105</v>
@@ -8157,7 +8169,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>106</v>
@@ -8198,10 +8210,10 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C24" s="4">
         <v>12.0</v>
@@ -8239,10 +8251,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C25" s="4">
         <v>9.0</v>
@@ -8280,10 +8292,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C26" s="4">
         <v>8.0</v>
@@ -8321,10 +8333,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4">
         <v>11.0</v>
@@ -8362,10 +8374,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4">
         <v>2.0</v>
@@ -8403,10 +8415,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C29" s="4">
         <v>4.0</v>
@@ -9437,21 +9449,21 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4">
         <v>45862.0</v>
@@ -9459,10 +9471,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C3" s="4">
         <v>37330.0</v>
@@ -9470,10 +9482,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4">
         <v>33645.0</v>
@@ -9481,10 +9493,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4">
         <v>33266.0</v>
@@ -9492,10 +9504,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4">
         <v>57771.0</v>
@@ -9503,10 +9515,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4">
         <v>2507.0</v>
@@ -9514,10 +9526,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="C8" s="4">
         <v>3902.0</v>
@@ -9525,10 +9537,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4">
         <v>493.0</v>
@@ -9536,10 +9548,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4">
         <v>583.0</v>
@@ -9547,10 +9559,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4">
         <v>7080.0</v>
@@ -10571,27 +10583,27 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B2" s="5">
         <v>1.86</v>
@@ -10611,7 +10623,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B3" s="5">
         <v>1.98</v>
@@ -10631,7 +10643,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B4" s="5">
         <v>2.54</v>
@@ -10651,7 +10663,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="5">
         <v>2.77</v>
@@ -10671,7 +10683,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B6" s="5">
         <v>1.94</v>
@@ -10691,7 +10703,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="5">
         <v>3.14</v>
@@ -10929,7 +10941,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="5">
         <v>5.53</v>
@@ -10949,7 +10961,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B20" s="5">
         <v>3.67</v>
@@ -10969,7 +10981,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B21" s="5">
         <v>7.01</v>
@@ -10989,7 +11001,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B22" s="5">
         <v>9.03</v>
@@ -11009,7 +11021,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B23" s="5">
         <v>4.72</v>
@@ -12027,15 +12039,15 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B2" s="4">
         <v>0.29</v>
@@ -12043,7 +12055,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B3" s="4">
         <v>0.28</v>
@@ -12051,7 +12063,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B4" s="5">
         <v>0.17</v>
@@ -12059,7 +12071,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B5" s="5">
         <v>0.13</v>
@@ -12067,7 +12079,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B6" s="4">
         <v>0.13</v>
@@ -13083,542 +13095,610 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="42.0"/>
-    <col customWidth="1" min="2" max="2" width="25.0"/>
-    <col customWidth="1" min="3" max="3" width="15.0"/>
-    <col customWidth="1" min="4" max="4" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="12.0"/>
-    <col customWidth="1" min="6" max="6" width="19.0"/>
-    <col customWidth="1" min="7" max="7" width="13.0"/>
-    <col customWidth="1" min="8" max="26" width="8.86"/>
+    <col customWidth="1" min="1" max="1" width="5.43"/>
+    <col customWidth="1" min="2" max="2" width="42.0"/>
+    <col customWidth="1" min="3" max="3" width="25.0"/>
+    <col customWidth="1" min="4" max="4" width="15.0"/>
+    <col customWidth="1" min="5" max="5" width="13.0"/>
+    <col customWidth="1" min="6" max="6" width="12.0"/>
+    <col customWidth="1" min="7" max="7" width="19.0"/>
+    <col customWidth="1" min="8" max="8" width="13.0"/>
+    <col customWidth="1" min="9" max="27" width="8.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>112</v>
+      <c r="H1" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="5">
+      <c r="C2" s="5">
+        <v>22.0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>4510.0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>6058.0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>4941.0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>6152.0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.93</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4886.0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4453.0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="5">
+        <v>53.0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9946.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>10626.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3518.0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3385.0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="5">
+        <v>65.0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>23.0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>13927.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>14675.0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="5">
+        <v>22.0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4347.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4774.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="5">
+        <v>32.0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>6432.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7100.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="5">
         <v>11.0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="D10" s="5">
         <v>10.0</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E10" s="5">
         <v>3148.0</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F10" s="5">
         <v>2801.0</v>
       </c>
-      <c r="F2" s="5">
+      <c r="G10" s="5">
         <v>0.6</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H10" s="5">
         <v>1.0</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="5">
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4846.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4255.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="5">
         <v>90.0</v>
       </c>
-      <c r="C3" s="5">
+      <c r="D12" s="5">
         <v>33.0</v>
       </c>
-      <c r="D3" s="5">
+      <c r="E12" s="5">
         <v>14178.0</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F12" s="5">
         <v>13744.0</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G12" s="5">
         <v>0.79</v>
       </c>
-      <c r="G3" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="H12" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5338.0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>5126.0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="5">
         <v>36.0</v>
       </c>
-      <c r="C4" s="5">
+      <c r="D14" s="5">
         <v>9.0</v>
       </c>
-      <c r="D4" s="5">
+      <c r="E14" s="5">
         <v>1930.0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F14" s="5">
         <v>1884.0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G14" s="5">
         <v>0.84</v>
       </c>
-      <c r="G4" s="5">
+      <c r="H14" s="5">
         <v>1.0</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="5">
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3722.0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>3074.0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="5">
         <v>22.0</v>
       </c>
-      <c r="C5" s="5">
-        <v>9.0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>4347.0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>4774.0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="D16" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3188.0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>3660.0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="H16" s="5">
         <v>1.0</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="5">
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="5">
+        <v>42.0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>9346.0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>10041.0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="5">
+        <v>27.0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>10503.0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>17449.0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="5">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="5">
+        <v>38.0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>4005.0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>3170.0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>6594.0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>5592.0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="5">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4726.0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3236.0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="5">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" s="5">
+        <v>17.0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>10200.0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6762.0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="5">
         <v>22.0</v>
       </c>
-      <c r="C6" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>3188.0</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3660.0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="5">
-        <v>38.0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4005.0</v>
-      </c>
-      <c r="E7" s="5">
-        <v>3170.0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.74</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="5">
-        <v>32.0</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B23" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="5">
+        <v>66.0</v>
+      </c>
+      <c r="D23" s="5">
         <v>6.0</v>
       </c>
-      <c r="D8" s="5">
-        <v>6432.0</v>
-      </c>
-      <c r="E8" s="5">
-        <v>7100.0</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="G8" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="C9" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5338.0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>5126.0</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10" s="5">
-        <v>24.0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>9.0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>4941.0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>6152.0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="5">
-        <v>22.0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>4510.0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>6058.0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="5">
-        <v>13.0</v>
-      </c>
-      <c r="C12" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3722.0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>3074.0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="C13" s="5">
-        <v>15.0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3518.0</v>
-      </c>
-      <c r="E13" s="5">
-        <v>3385.0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B14" s="5">
-        <v>65.0</v>
-      </c>
-      <c r="C14" s="5">
-        <v>23.0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>13927.0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>14675.0</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="5">
-        <v>53.0</v>
-      </c>
-      <c r="C15" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>9946.0</v>
-      </c>
-      <c r="E15" s="5">
-        <v>10626.0</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B16" s="5">
-        <v>31.0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>13.0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>4726.0</v>
-      </c>
-      <c r="E16" s="5">
-        <v>3236.0</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="C17" s="5">
-        <v>13.0</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4846.0</v>
-      </c>
-      <c r="E17" s="5">
-        <v>4255.0</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="G17" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="C18" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="D18" s="5">
-        <v>10200.0</v>
-      </c>
-      <c r="E18" s="5">
-        <v>6762.0</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B19" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="C19" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D19" s="5">
-        <v>4886.0</v>
-      </c>
-      <c r="E19" s="5">
-        <v>4453.0</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0.88</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B20" s="5">
-        <v>21.0</v>
-      </c>
-      <c r="C20" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="D20" s="5">
-        <v>6594.0</v>
-      </c>
-      <c r="E20" s="5">
-        <v>5592.0</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="5">
-        <v>42.0</v>
-      </c>
-      <c r="C21" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D21" s="5">
-        <v>9346.0</v>
-      </c>
-      <c r="E21" s="5">
-        <v>10041.0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="G21" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B22" s="5">
-        <v>27.0</v>
-      </c>
-      <c r="C22" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D22" s="5">
-        <v>10503.0</v>
-      </c>
-      <c r="E22" s="5">
-        <v>17449.0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B23" s="5">
-        <v>66.0</v>
-      </c>
-      <c r="C23" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="E23" s="5">
         <v>12426.0</v>
       </c>
-      <c r="E23" s="5">
+      <c r="F23" s="5">
         <v>2643.0</v>
       </c>
-      <c r="F23" s="5">
+      <c r="G23" s="5">
         <v>0.2</v>
       </c>
-      <c r="G23" s="5">
+      <c r="H23" s="5">
         <v>0.0</v>
       </c>
     </row>
@@ -14600,10 +14680,9 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$G$23">
-    <sortState ref="A1:G23">
+  <autoFilter ref="$A$1:$H$23">
+    <sortState ref="A1:H23">
       <sortCondition ref="A1:A23"/>
-      <sortCondition descending="1" ref="F1:F23"/>
     </sortState>
   </autoFilter>
   <printOptions/>
@@ -14631,36 +14710,36 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4">
         <v>0.98</v>
@@ -14687,7 +14766,7 @@
         <v>186</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4">
         <v>1.0</v>
@@ -14699,7 +14778,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>187</v>
       </c>
       <c r="G3" s="4" t="s">
@@ -14714,7 +14793,7 @@
         <v>189</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4">
         <v>1.0</v>
@@ -14741,7 +14820,7 @@
         <v>190</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4">
         <v>0.97</v>
@@ -14768,7 +14847,7 @@
         <v>192</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6" s="5">
         <v>0.95</v>
@@ -14792,10 +14871,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" s="5">
         <v>0.71</v>
@@ -14808,7 +14887,7 @@
         <v>0.455</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>185</v>
@@ -14819,10 +14898,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4">
         <v>0.15</v>
@@ -14835,7 +14914,7 @@
         <v>0.075</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>185</v>
@@ -14846,10 +14925,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C9" s="4">
         <v>0.15</v>
@@ -14862,7 +14941,7 @@
         <v>0.075</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>185</v>
@@ -14873,10 +14952,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C10" s="4">
         <v>0.0</v>
@@ -14900,10 +14979,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C11" s="4">
         <v>0.0</v>
@@ -14916,7 +14995,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>185</v>
@@ -14927,10 +15006,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C12" s="4">
         <v>0.0</v>
@@ -14943,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>185</v>
@@ -14954,10 +15033,10 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C13" s="4">
         <v>0.0</v>
@@ -14970,7 +15049,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>185</v>
@@ -14981,10 +15060,10 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C14" s="4">
         <v>0.0</v>
@@ -14997,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>185</v>
@@ -15008,10 +15087,10 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C15" s="4">
         <v>0.0</v>
@@ -15024,7 +15103,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>185</v>
@@ -15035,10 +15114,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C16" s="4">
         <v>0.0</v>
@@ -15051,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>185</v>
@@ -15062,10 +15141,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C17" s="4">
         <v>0.0</v>
@@ -15078,7 +15157,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>185</v>
@@ -15089,10 +15168,10 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C18" s="4">
         <v>0.0</v>
@@ -15105,7 +15184,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>185</v>
@@ -15116,10 +15195,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C19" s="4">
         <v>0.0</v>
@@ -15132,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>185</v>
@@ -15143,10 +15222,10 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C20" s="4">
         <v>0.0</v>
@@ -15159,7 +15238,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>185</v>
@@ -16167,13 +16246,13 @@
     <col customWidth="1" min="1" max="1" width="24.0"/>
     <col customWidth="1" min="2" max="2" width="21.0"/>
     <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="12" width="10.0"/>
-    <col customWidth="1" min="13" max="26" width="8.86"/>
+    <col customWidth="1" min="4" max="14" width="10.0"/>
+    <col customWidth="1" min="15" max="28" width="8.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>193</v>
@@ -16182,39 +16261,45 @@
         <v>194</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>197</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>202</v>
       </c>
+      <c r="I1" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="J1" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+        <v>218</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
       <c r="D2" s="4">
         <v>0.0</v>
       </c>
@@ -16227,28 +16312,34 @@
       <c r="G2" s="4">
         <v>0.0</v>
       </c>
-      <c r="H2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.0</v>
+      <c r="H2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>3.0</v>
       </c>
       <c r="L2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="N2" s="4">
         <v>4.0</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
+        <v>222</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="4">
         <v>0.0</v>
       </c>
@@ -16261,28 +16352,34 @@
       <c r="G3" s="4">
         <v>7.0</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="K3" s="5">
         <v>18.0</v>
       </c>
-      <c r="I3" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>6.0</v>
       </c>
-      <c r="L3" s="4">
-        <v>44.0</v>
+      <c r="M3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>42.0</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+        <v>225</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="4">
         <v>3.0</v>
       </c>
@@ -16295,28 +16392,34 @@
       <c r="G4" s="4">
         <v>2.0</v>
       </c>
-      <c r="H4" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="H4" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="M4" s="5">
         <v>1.0</v>
       </c>
-      <c r="J4" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>19.0</v>
+      <c r="N4" s="5">
+        <v>18.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
+        <v>227</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="4">
         <v>1.0</v>
       </c>
@@ -16329,28 +16432,34 @@
       <c r="G5" s="4">
         <v>3.0</v>
       </c>
-      <c r="H5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>12.0</v>
+      <c r="H5" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>11.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
+        <v>229</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="4">
         <v>3.0</v>
       </c>
@@ -16363,28 +16472,34 @@
       <c r="G6" s="4">
         <v>3.0</v>
       </c>
-      <c r="H6" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>1.0</v>
+      <c r="H6" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.0</v>
       </c>
       <c r="J6" s="4">
         <v>1.0</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="M6" s="5">
         <v>1.0</v>
       </c>
-      <c r="L6" s="4">
-        <v>15.0</v>
+      <c r="N6" s="5">
+        <v>13.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="4">
         <v>0.0</v>
       </c>
@@ -16397,28 +16512,34 @@
       <c r="G7" s="4">
         <v>2.0</v>
       </c>
-      <c r="H7" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="H7" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J7" s="4">
         <v>1.0</v>
       </c>
-      <c r="J7" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="K7" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="M7" s="5">
         <v>1.0</v>
       </c>
-      <c r="L7" s="4">
-        <v>13.0</v>
+      <c r="N7" s="5">
+        <v>12.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+        <v>234</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="4">
         <v>0.0</v>
       </c>
@@ -16431,28 +16552,34 @@
       <c r="G8" s="4">
         <v>0.0</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="5">
         <v>1.0</v>
       </c>
-      <c r="I8" s="4">
+      <c r="L8" s="5">
         <v>1.0</v>
       </c>
-      <c r="J8" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="4">
-        <v>4.0</v>
+      <c r="M8" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3.0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+        <v>236</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="4">
         <v>7.0</v>
       </c>
@@ -16465,28 +16592,34 @@
       <c r="G9" s="4">
         <v>5.0</v>
       </c>
-      <c r="H9" s="4">
-        <v>26.0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="J9" s="4">
+      <c r="H9" s="5">
         <v>3.0</v>
       </c>
-      <c r="K9" s="4">
+      <c r="I9" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="L9" s="4">
         <v>7.0</v>
       </c>
-      <c r="L9" s="4">
-        <v>65.0</v>
+      <c r="M9" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>63.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+        <v>237</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="4">
         <v>3.0</v>
       </c>
@@ -16499,28 +16632,34 @@
       <c r="G10" s="4">
         <v>1.0</v>
       </c>
-      <c r="H10" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="4">
-        <v>13.0</v>
+      <c r="H10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>12.0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
+        <v>238</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="4">
         <v>2.0</v>
       </c>
@@ -16533,28 +16672,34 @@
       <c r="G11" s="4">
         <v>1.0</v>
       </c>
-      <c r="H11" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="H11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J11" s="5">
         <v>2.0</v>
       </c>
-      <c r="L11" s="4">
-        <v>14.0</v>
+      <c r="K11" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>13.0</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="4">
         <v>5.0</v>
       </c>
@@ -16567,28 +16712,34 @@
       <c r="G12" s="4">
         <v>1.0</v>
       </c>
-      <c r="H12" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="H12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="L12" s="5">
         <v>2.0</v>
       </c>
-      <c r="J12" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="4">
+      <c r="M12" s="5">
         <v>1.0</v>
       </c>
-      <c r="L12" s="4">
+      <c r="N12" s="4">
         <v>14.0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
+        <v>240</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="4">
         <v>2.0</v>
       </c>
@@ -16601,28 +16752,34 @@
       <c r="G13" s="4">
         <v>1.0</v>
       </c>
-      <c r="H13" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="I13" s="4">
+      <c r="H13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="5">
         <v>2.0</v>
       </c>
-      <c r="J13" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="J13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="M13" s="5">
         <v>1.0</v>
       </c>
-      <c r="L13" s="4">
-        <v>15.0</v>
+      <c r="N13" s="5">
+        <v>14.0</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="4">
         <v>0.0</v>
       </c>
@@ -16635,28 +16792,34 @@
       <c r="G14" s="4">
         <v>0.0</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="5">
         <v>1.0</v>
       </c>
-      <c r="I14" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="4">
+      <c r="L14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N14" s="4">
         <v>4.0</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+        <v>242</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="4">
         <v>1.0</v>
       </c>
@@ -16669,28 +16832,34 @@
       <c r="G15" s="4">
         <v>1.0</v>
       </c>
-      <c r="H15" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="I15" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="4">
+      <c r="H15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="5">
         <v>1.0</v>
       </c>
+      <c r="J15" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>3.0</v>
+      </c>
       <c r="L15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="4">
         <v>13.0</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+        <v>243</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="4">
         <v>0.0</v>
       </c>
@@ -16703,28 +16872,34 @@
       <c r="G16" s="4">
         <v>0.0</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="5">
         <v>1.0</v>
       </c>
-      <c r="I16" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="4">
+      <c r="L16" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N16" s="4">
         <v>4.0</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+        <v>244</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="4">
         <v>1.0</v>
       </c>
@@ -16737,28 +16912,34 @@
       <c r="G17" s="4">
         <v>2.0</v>
       </c>
-      <c r="H17" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="I17" s="4">
+      <c r="H17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="5">
         <v>2.0</v>
       </c>
       <c r="J17" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K17" s="4">
         <v>1.0</v>
       </c>
-      <c r="L17" s="4">
-        <v>13.0</v>
+      <c r="L17" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>12.0</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="4">
         <v>0.0</v>
       </c>
@@ -16775,21 +16956,27 @@
         <v>0.0</v>
       </c>
       <c r="I18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="5">
         <v>1.0</v>
       </c>
-      <c r="J18" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="4">
-        <v>0.0</v>
-      </c>
       <c r="L18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
     </row>
     <row r="20" ht="14.25" customHeight="1"/>
     <row r="21" ht="14.25" customHeight="1"/>
@@ -17773,7 +17960,7 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$L$18"/>
+  <autoFilter ref="$A$1:$N$18"/>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/BD_dashboard_operaciones_github.xlsx
+++ b/BD_dashboard_operaciones_github.xlsx
@@ -50,141 +50,171 @@
     <t>El HTML ya está programado para leer el archivo 'BD_dashboard_operaciones_github.xlsx' de forma automática al abrirse.</t>
   </si>
   <si>
+    <t>periodo</t>
+  </si>
+  <si>
+    <t>modulo</t>
+  </si>
+  <si>
+    <t>CÓMO USARLO:</t>
+  </si>
+  <si>
+    <t>1. Edita los valores en las hojas de abajo (no cambies los nombres de hoja ni de columnas).</t>
+  </si>
+  <si>
+    <t>2. Guarda este archivo con el nombre exacto: BD_dashboard_operaciones_github.xlsx</t>
+  </si>
+  <si>
+    <t>3. Súbelo a la misma carpeta/repositorio donde está el index.html (reemplazando el anterior).</t>
+  </si>
+  <si>
+    <t>4. Al abrir o recargar el HTML, los datos se actualizan solos (no hay que tocar el código).</t>
+  </si>
+  <si>
     <t>zona</t>
   </si>
   <si>
-    <t>CÓMO USARLO:</t>
-  </si>
-  <si>
-    <t>1. Edita los valores en las hojas de abajo (no cambies los nombres de hoja ni de columnas).</t>
-  </si>
-  <si>
-    <t>modulo</t>
-  </si>
-  <si>
-    <t>2. Guarda este archivo con el nombre exacto: BD_dashboard_operaciones_github.xlsx</t>
-  </si>
-  <si>
-    <t>3. Súbelo a la misma carpeta/repositorio donde está el index.html (reemplazando el anterior).</t>
-  </si>
-  <si>
-    <t>4. Al abrir o recargar el HTML, los datos se actualizan solos (no hay que tocar el código).</t>
+    <t>HOJAS Y SU FUNCIÓN:</t>
+  </si>
+  <si>
+    <t>KPIs_HTML: todas las tarjetas numéricas (KPI) del dashboard. Columnas: modulo, indicador, valor, unidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   unidad admite: porcentaje (valor como fracción, ej. 0.95 = 95%), entero, minutos, moneda, decimal.</t>
+  </si>
+  <si>
+    <t>LIMPIEZA_COBERTURA: tabla de cobertura de limpieza por sede.</t>
+  </si>
+  <si>
+    <t>LIMPIEZA_PRESUPUESTO: montos mensuales de descuentos y penalidades. periodo en formato AAAA-MM.</t>
+  </si>
+  <si>
+    <t>indicador</t>
+  </si>
+  <si>
+    <t>AULA911_CAMPUS: tiempos de atención y valoración por campus (Aula 911).</t>
+  </si>
+  <si>
+    <t>AULA911_TOP: participación (fracción 0-1) de los tipos de incidencia más frecuentes.</t>
   </si>
   <si>
     <t>campus</t>
   </si>
   <si>
-    <t>HOJAS Y SU FUNCIÓN:</t>
-  </si>
-  <si>
-    <t>indicador</t>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>RONDAS: cumplimiento de rondas por sede.</t>
+  </si>
+  <si>
+    <t>PROYECTOS: portafolio de proyectos 2026 (usado también en el detalle de Huánuco/Huamanga/Juliaca).</t>
+  </si>
+  <si>
+    <t>unidad</t>
   </si>
   <si>
     <t>dot_m</t>
   </si>
   <si>
-    <t>KPIs_HTML: todas las tarjetas numéricas (KPI) del dashboard. Columnas: modulo, indicador, valor, unidad.</t>
-  </si>
-  <si>
-    <t>valor</t>
+    <t>MEJORAS_PROGRAMACION: iniciativas estratégicas por campus y mes.</t>
+  </si>
+  <si>
+    <t>MEJORAS_ESTADO: conteo de iniciativas por estado (Ejecutado/En proceso/Pendiente/Cancelado).</t>
+  </si>
+  <si>
+    <t>concepto</t>
+  </si>
+  <si>
+    <t>Limpieza</t>
   </si>
   <si>
     <t>dot_t</t>
   </si>
   <si>
-    <t>unidad</t>
+    <t>LISTO: implementación del programa Listo por campus (incluye el detalle de Trujillo).</t>
+  </si>
+  <si>
+    <t>CONFIG_HTML (opcional): permite sobrescribir textos puntuales del HTML por selector CSS.</t>
+  </si>
+  <si>
+    <t>monto</t>
   </si>
   <si>
     <t>dot_n</t>
   </si>
   <si>
-    <t>Limpieza</t>
+    <t xml:space="preserve">   selector 'meta:&lt;id-seccion&gt;:eyebrow' o 'meta:&lt;id-seccion&gt;:title' cambia los títulos de cada sección.</t>
+  </si>
+  <si>
+    <t>Cobertura semanal total</t>
   </si>
   <si>
     <t>cob_m</t>
   </si>
   <si>
+    <t>porcentaje</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
     <t>cob_t</t>
   </si>
   <si>
+    <t>Descuentos faltas/tardanzas</t>
+  </si>
+  <si>
     <t>cob_n</t>
   </si>
   <si>
+    <t>Dotación programada (turnos)</t>
+  </si>
+  <si>
+    <t>entero</t>
+  </si>
+  <si>
     <t>pend_m</t>
   </si>
   <si>
+    <t>2026-06</t>
+  </si>
+  <si>
     <t>pend_t</t>
   </si>
   <si>
-    <t xml:space="preserve">   unidad admite: porcentaje (valor como fracción, ej. 0.95 = 95%), entero, minutos, moneda, decimal.</t>
-  </si>
-  <si>
-    <t>Cobertura semanal total</t>
+    <t>Turnos cubiertos</t>
   </si>
   <si>
     <t>pend_n</t>
   </si>
   <si>
-    <t>LIMPIEZA_COBERTURA: tabla de cobertura de limpieza por sede.</t>
+    <t>2026-07</t>
   </si>
   <si>
     <t>pend_total</t>
   </si>
   <si>
-    <t>LIMPIEZA_PRESUPUESTO: montos mensuales de descuentos y penalidades. periodo en formato AAAA-MM.</t>
-  </si>
-  <si>
     <t>cobertura_pct</t>
   </si>
   <si>
-    <t>AULA911_CAMPUS: tiempos de atención y valoración por campus (Aula 911).</t>
-  </si>
-  <si>
-    <t>AULA911_TOP: participación (fracción 0-1) de los tipos de incidencia más frecuentes.</t>
-  </si>
-  <si>
-    <t>RONDAS: cumplimiento de rondas por sede.</t>
-  </si>
-  <si>
-    <t>PROYECTOS: portafolio de proyectos 2026 (usado también en el detalle de Huánuco/Huamanga/Juliaca).</t>
+    <t>2026-08</t>
   </si>
   <si>
     <t>LIMA</t>
   </si>
   <si>
-    <t>MEJORAS_PROGRAMACION: iniciativas estratégicas por campus y mes.</t>
-  </si>
-  <si>
-    <t>porcentaje</t>
-  </si>
-  <si>
-    <t>MEJORAS_ESTADO: conteo de iniciativas por estado (Ejecutado/En proceso/Pendiente/Cancelado).</t>
+    <t>2026-09</t>
   </si>
   <si>
     <t>SJL I</t>
   </si>
   <si>
-    <t>Dotación programada (turnos)</t>
-  </si>
-  <si>
-    <t>LISTO: implementación del programa Listo por campus (incluye el detalle de Trujillo).</t>
-  </si>
-  <si>
-    <t>entero</t>
-  </si>
-  <si>
-    <t>CONFIG_HTML (opcional): permite sobrescribir textos puntuales del HTML por selector CSS.</t>
-  </si>
-  <si>
-    <t>Turnos cubiertos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   selector 'meta:&lt;id-seccion&gt;:eyebrow' o 'meta:&lt;id-seccion&gt;:title' cambia los títulos de cada sección.</t>
-  </si>
-  <si>
     <t>Turnos pendientes</t>
   </si>
   <si>
+    <t>Penalidades</t>
+  </si>
+  <si>
     <t>Presupuesto 2026</t>
   </si>
   <si>
@@ -197,12 +227,12 @@
     <t>ALMACEN CENTRAL</t>
   </si>
   <si>
-    <t>periodo</t>
-  </si>
-  <si>
     <t>Nivel de ejecución</t>
   </si>
   <si>
+    <t>JARRITA</t>
+  </si>
+  <si>
     <t>Descuentos + penalidades</t>
   </si>
   <si>
@@ -212,16 +242,16 @@
     <t># incidencias</t>
   </si>
   <si>
+    <t>TORRE NUEVA</t>
+  </si>
+  <si>
     <t>Tiempo acepta solicitud</t>
   </si>
   <si>
     <t>minutos</t>
   </si>
   <si>
-    <t>JARRITA</t>
-  </si>
-  <si>
-    <t>concepto</t>
+    <t>LIMA NORTE</t>
   </si>
   <si>
     <t>Tiempo atiende solicitud</t>
@@ -230,7 +260,10 @@
     <t>Tiempo total de atención</t>
   </si>
   <si>
-    <t>monto</t>
+    <t>PROVINCIA</t>
+  </si>
+  <si>
+    <t>AREQUIPA POSTGRADO</t>
   </si>
   <si>
     <t>Valoración general</t>
@@ -239,64 +272,43 @@
     <t>decimal</t>
   </si>
   <si>
-    <t>2026-05</t>
-  </si>
-  <si>
     <t>Rondas</t>
   </si>
   <si>
     <t>% cumplimiento</t>
   </si>
   <si>
-    <t>Descuentos faltas/tardanzas</t>
+    <t>CHIMBOTE</t>
   </si>
   <si>
     <t>% cumplimiento encargado</t>
   </si>
   <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>TORRE NUEVA</t>
-  </si>
-  <si>
     <t>% cumplimiento Asistente</t>
   </si>
   <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>LIMA NORTE</t>
+    <t>PIURA</t>
   </si>
   <si>
     <t>Total programado</t>
   </si>
   <si>
-    <t>2026-08</t>
-  </si>
-  <si>
     <t>Total ejecutado</t>
   </si>
   <si>
-    <t>2026-09</t>
-  </si>
-  <si>
     <t># checkpoints</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>Proyectos</t>
   </si>
   <si>
-    <t>Penalidades</t>
-  </si>
-  <si>
-    <t>PROVINCIA</t>
-  </si>
-  <si>
     <t>En proceso</t>
   </si>
   <si>
-    <t>AREQUIPA POSTGRADO</t>
+    <t>HUANCAYO</t>
   </si>
   <si>
     <t>Pendientes</t>
@@ -308,27 +320,15 @@
     <t>Registros</t>
   </si>
   <si>
+    <t>HUANUCO</t>
+  </si>
+  <si>
     <t>Operativos</t>
   </si>
   <si>
     <t>Por implementar</t>
   </si>
   <si>
-    <t>CHIMBOTE</t>
-  </si>
-  <si>
-    <t>PIURA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HUANCAYO</t>
-  </si>
-  <si>
-    <t>HUANUCO</t>
-  </si>
-  <si>
     <t>IQUITOS</t>
   </si>
   <si>
@@ -371,33 +371,33 @@
     <t>AREQUIPA III</t>
   </si>
   <si>
+    <t>tiempo_acepta_min</t>
+  </si>
+  <si>
+    <t>tiempo_atiende_min</t>
+  </si>
+  <si>
     <t>AREQUIPA II</t>
   </si>
   <si>
+    <t>tiempo_total_min</t>
+  </si>
+  <si>
+    <t>valoracion</t>
+  </si>
+  <si>
+    <t>es_subsede</t>
+  </si>
+  <si>
     <t>EPG SALAVERRY</t>
   </si>
   <si>
+    <t>CAMPUS CHIMBOTE</t>
+  </si>
+  <si>
     <t>JOSE DIAZ</t>
   </si>
   <si>
-    <t>tiempo_acepta_min</t>
-  </si>
-  <si>
-    <t>tiempo_atiende_min</t>
-  </si>
-  <si>
-    <t>tiempo_total_min</t>
-  </si>
-  <si>
-    <t>valoracion</t>
-  </si>
-  <si>
-    <t>es_subsede</t>
-  </si>
-  <si>
-    <t>CAMPUS CHIMBOTE</t>
-  </si>
-  <si>
     <t>CAMPUS TRUJILLO</t>
   </si>
   <si>
@@ -446,60 +446,60 @@
     <t>Sede Central</t>
   </si>
   <si>
+    <t>CAMPUS ICA</t>
+  </si>
+  <si>
+    <t>CAMPUS TACNA</t>
+  </si>
+  <si>
+    <t>CAMPUS PUCALLPA</t>
+  </si>
+  <si>
+    <t>CAMPUS LIMA NORTE UTP</t>
+  </si>
+  <si>
+    <t>CAMPUS LIMA SUR UTP</t>
+  </si>
+  <si>
     <t>tipo_incidencia</t>
   </si>
   <si>
-    <t>CAMPUS ICA</t>
-  </si>
-  <si>
     <t>participacion</t>
   </si>
   <si>
-    <t>CAMPUS TACNA</t>
-  </si>
-  <si>
     <t>Problema con la PC</t>
   </si>
   <si>
+    <t>sede</t>
+  </si>
+  <si>
     <t>Problema con el proyector</t>
   </si>
   <si>
-    <t>CAMPUS PUCALLPA</t>
+    <t>dispositivos_asignados</t>
   </si>
   <si>
     <t>Ambiente cerrado</t>
   </si>
   <si>
-    <t>CAMPUS LIMA NORTE UTP</t>
+    <t>responsables</t>
+  </si>
+  <si>
+    <t>programado</t>
+  </si>
+  <si>
+    <t>ejecutado</t>
   </si>
   <si>
     <t>Problema con el audio</t>
   </si>
   <si>
+    <t>cumplimiento_pct</t>
+  </si>
+  <si>
     <t>Problema con el Zoom</t>
   </si>
   <si>
-    <t>CAMPUS LIMA SUR UTP</t>
-  </si>
-  <si>
-    <t>sede</t>
-  </si>
-  <si>
-    <t>dispositivos_asignados</t>
-  </si>
-  <si>
-    <t>responsables</t>
-  </si>
-  <si>
-    <t>programado</t>
-  </si>
-  <si>
-    <t>ejecutado</t>
-  </si>
-  <si>
-    <t>cumplimiento_pct</t>
-  </si>
-  <si>
     <t>04. UTP Ate</t>
   </si>
   <si>
@@ -545,42 +545,42 @@
     <t>02. UTP Lima Centro Torre Arequipa</t>
   </si>
   <si>
+    <t>proyecto</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
     <t>13. UTP Iquitos</t>
   </si>
   <si>
-    <t>proyecto</t>
-  </si>
-  <si>
-    <t>estado</t>
+    <t>avance_obra_pct</t>
+  </si>
+  <si>
+    <t>avance_compras_pct</t>
+  </si>
+  <si>
+    <t>avance_implementación_pct</t>
+  </si>
+  <si>
+    <t>fecha_objetivo_texto</t>
   </si>
   <si>
     <t>14. UTP Pucallpa</t>
   </si>
   <si>
-    <t>avance_obra_pct</t>
-  </si>
-  <si>
-    <t>avance_compras_pct</t>
-  </si>
-  <si>
-    <t>avance_implementación_pct</t>
-  </si>
-  <si>
-    <t>fecha_objetivo_texto</t>
+    <t>con_observaciones</t>
+  </si>
+  <si>
+    <t>nueva_fecha_texto</t>
+  </si>
+  <si>
+    <t>Nuevo Edificio Campus Lima Norte (Salud) – Por definir ITSE</t>
   </si>
   <si>
     <t>02. UTP Lima Norte</t>
   </si>
   <si>
-    <t>con_observaciones</t>
-  </si>
-  <si>
-    <t>nueva_fecha_texto</t>
-  </si>
-  <si>
-    <t>Nuevo Edificio Campus Lima Norte (Salud) – Por definir ITSE</t>
-  </si>
-  <si>
     <t>12. UTP Trujillo</t>
   </si>
   <si>
@@ -590,15 +590,15 @@
     <t>10. UTP Chimbote</t>
   </si>
   <si>
+    <t>SET 26</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>15. UTP Tacna</t>
   </si>
   <si>
-    <t>SET 26</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Laboratorios Salud Campus Lima Norte – ETAPA I – Pendiente ITSE</t>
   </si>
   <si>
@@ -620,43 +620,67 @@
     <t>Nuevo Campus Huamanga – ITSE – 02/10</t>
   </si>
   <si>
+    <t>Nuevo Campus Juliaca – ITSE - 18/11</t>
+  </si>
+  <si>
+    <t>NOV 26</t>
+  </si>
+  <si>
+    <t>Nuevos Laboratorios de Hotelería y Turismo – Lima Centro</t>
+  </si>
+  <si>
+    <t>ENE 27</t>
+  </si>
+  <si>
+    <t>Nuevos Laboratorios de Odontología – Lima Centro - Jarrita</t>
+  </si>
+  <si>
+    <t>MAR 27</t>
+  </si>
+  <si>
     <t>fecha_inicio_texto</t>
   </si>
   <si>
+    <t>Nuevo Campus Cusco</t>
+  </si>
+  <si>
     <t>fecha_fin_texto</t>
   </si>
   <si>
-    <t>Nuevo Campus Juliaca – ITSE - 18/11</t>
+    <t>Pendiente</t>
   </si>
   <si>
     <t>mar</t>
   </si>
   <si>
+    <t>JUL 27</t>
+  </si>
+  <si>
+    <t>Ampliación Campus Huancayo</t>
+  </si>
+  <si>
     <t>abr</t>
   </si>
   <si>
-    <t>NOV 26</t>
-  </si>
-  <si>
     <t>may</t>
   </si>
   <si>
-    <t>Nuevos Laboratorios de Hotelería y Turismo – Lima Centro</t>
+    <t>AGO 27</t>
   </si>
   <si>
     <t>jun</t>
   </si>
   <si>
+    <t>Ampliación Campus Piura</t>
+  </si>
+  <si>
     <t>jul</t>
   </si>
   <si>
-    <t>ENE 27</t>
-  </si>
-  <si>
-    <t>Nuevos Laboratorios de Odontología – Lima Centro - Jarrita</t>
-  </si>
-  <si>
-    <t>MAR 27</t>
+    <t>Remodelación de Saco Oliveros</t>
+  </si>
+  <si>
+    <t>Clínica Odontológica – Guzman Blanco</t>
   </si>
   <si>
     <t>agos</t>
@@ -665,90 +689,66 @@
     <t>set</t>
   </si>
   <si>
-    <t>Nuevo Campus Cusco</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
     <t>oct</t>
   </si>
   <si>
+    <t>Idat Campus SJL</t>
+  </si>
+  <si>
     <t>nov</t>
   </si>
   <si>
+    <t>dic</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Idat Campus SJM</t>
+  </si>
+  <si>
+    <t>Corporativo - Natalio</t>
+  </si>
+  <si>
+    <t>UTP Arequipa</t>
+  </si>
+  <si>
+    <t>UTP Chiclayo</t>
+  </si>
+  <si>
+    <t>Idat Chiclayo</t>
+  </si>
+  <si>
+    <t>UTP Chimbote</t>
+  </si>
+  <si>
+    <t>Medicina Ica</t>
+  </si>
+  <si>
+    <t>UTP Huancayo</t>
+  </si>
+  <si>
+    <t>Medicina Trujillo</t>
+  </si>
+  <si>
     <t>cantidad</t>
   </si>
   <si>
-    <t>JUL 27</t>
-  </si>
-  <si>
-    <t>dic</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>Ampliación Campus Huancayo</t>
+    <t>UTP Ica</t>
+  </si>
+  <si>
+    <t>Medicina Piura</t>
   </si>
   <si>
     <t>Ejecutado</t>
   </si>
   <si>
-    <t>Corporativo - Natalio</t>
-  </si>
-  <si>
-    <t>AGO 27</t>
-  </si>
-  <si>
-    <t>Ampliación Campus Piura</t>
-  </si>
-  <si>
-    <t>Remodelación de Saco Oliveros</t>
-  </si>
-  <si>
-    <t>UTP Arequipa</t>
+    <t>UTP Iquitos</t>
   </si>
   <si>
     <t>Cancelado</t>
   </si>
   <si>
-    <t>Clínica Odontológica – Guzman Blanco</t>
-  </si>
-  <si>
-    <t>UTP Chiclayo</t>
-  </si>
-  <si>
-    <t>Idat Campus SJL</t>
-  </si>
-  <si>
-    <t>UTP Chimbote</t>
-  </si>
-  <si>
-    <t>Idat Campus SJM</t>
-  </si>
-  <si>
-    <t>UTP Huancayo</t>
-  </si>
-  <si>
-    <t>Idat Chiclayo</t>
-  </si>
-  <si>
-    <t>UTP Ica</t>
-  </si>
-  <si>
-    <t>Medicina Ica</t>
-  </si>
-  <si>
-    <t>Medicina Trujillo</t>
-  </si>
-  <si>
-    <t>UTP Iquitos</t>
-  </si>
-  <si>
-    <t>Medicina Piura</t>
-  </si>
-  <si>
     <t>UTP Lima Centro</t>
   </si>
   <si>
@@ -782,22 +782,22 @@
     <t>diseno_pct</t>
   </si>
   <si>
+    <t>obra_pct</t>
+  </si>
+  <si>
     <t>selector</t>
   </si>
   <si>
-    <t>obra_pct</t>
+    <t>operacion</t>
+  </si>
+  <si>
+    <t>con_observacion</t>
   </si>
   <si>
     <t>tipo</t>
   </si>
   <si>
-    <t>operacion</t>
-  </si>
-  <si>
     <t>atributo</t>
-  </si>
-  <si>
-    <t>con_observacion</t>
   </si>
   <si>
     <t>LC – Torre Tecnológica Arequipa (I)</t>
@@ -1261,12 +1261,12 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -1294,67 +1294,67 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1"/>
@@ -2356,18 +2356,18 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B2" s="4">
         <v>80.0</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B3" s="4">
         <v>111.0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B4" s="4">
         <v>76.0</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B5" s="4">
         <v>27.0</v>
@@ -3432,25 +3432,25 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>246</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -3473,7 +3473,7 @@
         <v>256</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -3519,7 +3519,7 @@
         <v>256</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -3542,7 +3542,7 @@
         <v>256</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -3565,7 +3565,7 @@
         <v>256</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -3588,7 +3588,7 @@
         <v>256</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
@@ -3611,7 +3611,7 @@
         <v>256</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
@@ -3703,7 +3703,7 @@
         <v>256</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
@@ -3717,16 +3717,16 @@
         <v>0.0</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
@@ -3740,16 +3740,16 @@
         <v>0.0</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>273</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
@@ -3763,7 +3763,7 @@
         <v>0.4</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>273</v>
@@ -3782,16 +3782,16 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>276</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
@@ -3805,16 +3805,16 @@
         <v>0.0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>276</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
@@ -3828,16 +3828,16 @@
         <v>0.0</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>276</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
@@ -3851,16 +3851,16 @@
         <v>0.0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1"/>
@@ -4869,16 +4869,16 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1"/>
@@ -5905,38 +5905,38 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4">
         <v>0.95</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="4">
         <v>616.0</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4">
         <v>584.0</v>
@@ -5961,10 +5961,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C5" s="4">
         <v>32.0</v>
@@ -5975,66 +5975,66 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4">
         <v>1.8E7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C7" s="4">
         <v>1.12E7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4">
         <v>0.622</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C9" s="4">
         <v>222439.0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4">
         <v>21040.0</v>
@@ -6045,108 +6045,108 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C11" s="4">
         <v>4.7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4">
         <v>4.7</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C13" s="4">
         <v>9.4</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4">
         <v>4.6</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C15" s="4">
         <v>0.71</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C16" s="4">
         <v>0.57</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C17" s="4">
         <v>0.77</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C18" s="4">
         <v>106191.0</v>
@@ -6157,10 +6157,10 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C19" s="4">
         <v>97422.0</v>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C20" s="4">
         <v>678.0</v>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C21" s="4">
         <v>19.0</v>
@@ -6199,10 +6199,10 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" s="4">
         <v>8.0</v>
@@ -6213,10 +6213,10 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C23" s="4">
         <v>11.0</v>
@@ -6227,10 +6227,10 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C24" s="4">
         <v>18.0</v>
@@ -6241,10 +6241,10 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C25" s="4">
         <v>11.0</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C26" s="4">
         <v>7.0</v>
@@ -7267,51 +7267,51 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4">
         <v>9.0</v>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C3" s="4">
         <v>1.0</v>
@@ -7390,10 +7390,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4">
         <v>3.0</v>
@@ -7431,10 +7431,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C5" s="4">
         <v>15.0</v>
@@ -7472,10 +7472,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4">
         <v>19.0</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4">
         <v>1.0</v>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4">
         <v>16.0</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4">
         <v>15.0</v>
@@ -7636,10 +7636,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C10" s="4">
         <v>8.0</v>
@@ -7677,10 +7677,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4">
         <v>13.0</v>
@@ -7718,10 +7718,10 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4">
         <v>1.0</v>
@@ -7759,7 +7759,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>96</v>
@@ -7800,7 +7800,7 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>97</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>98</v>
@@ -7882,7 +7882,7 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>99</v>
@@ -7923,7 +7923,7 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>100</v>
@@ -7964,7 +7964,7 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>101</v>
@@ -8005,7 +8005,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>102</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>103</v>
@@ -8087,7 +8087,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>104</v>
@@ -8128,7 +8128,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>105</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>106</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>107</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>108</v>
@@ -8292,7 +8292,7 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>109</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C27" s="4">
         <v>11.0</v>
@@ -8374,10 +8374,10 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C28" s="4">
         <v>2.0</v>
@@ -8415,10 +8415,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C29" s="4">
         <v>4.0</v>
@@ -9449,21 +9449,21 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C2" s="4">
         <v>45862.0</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4">
         <v>37330.0</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4">
         <v>33645.0</v>
@@ -9493,10 +9493,10 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C5" s="4">
         <v>33266.0</v>
@@ -9504,10 +9504,10 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4">
         <v>57771.0</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4">
         <v>2507.0</v>
@@ -9526,10 +9526,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4">
         <v>3902.0</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4">
         <v>493.0</v>
@@ -9548,10 +9548,10 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4">
         <v>583.0</v>
@@ -9559,10 +9559,10 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4">
         <v>7080.0</v>
@@ -10583,27 +10583,27 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B2" s="5">
         <v>1.86</v>
@@ -10941,7 +10941,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B19" s="5">
         <v>5.53</v>
@@ -10961,7 +10961,7 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B20" s="5">
         <v>3.67</v>
@@ -10981,7 +10981,7 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B21" s="5">
         <v>7.01</v>
@@ -11001,7 +11001,7 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B22" s="5">
         <v>9.03</v>
@@ -11021,7 +11021,7 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B23" s="5">
         <v>4.72</v>
@@ -12039,15 +12039,15 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B2" s="4">
         <v>0.29</v>
@@ -12055,7 +12055,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B3" s="4">
         <v>0.28</v>
@@ -12063,7 +12063,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B4" s="5">
         <v>0.17</v>
@@ -12071,7 +12071,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B5" s="5">
         <v>0.13</v>
@@ -12079,7 +12079,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B6" s="4">
         <v>0.13</v>
@@ -13109,25 +13109,25 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="6"/>
       <c r="B1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -13525,7 +13525,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C17" s="5">
         <v>42.0</v>
@@ -13551,7 +13551,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C18" s="5">
         <v>27.0</v>
@@ -13577,7 +13577,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C19" s="5">
         <v>38.0</v>
@@ -13681,7 +13681,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C23" s="5">
         <v>66.0</v>
@@ -14710,36 +14710,36 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="C1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="G1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4">
         <v>0.98</v>
@@ -14752,13 +14752,13 @@
         <v>0.965</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -14766,7 +14766,7 @@
         <v>186</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C3" s="4">
         <v>1.0</v>
@@ -14785,7 +14785,7 @@
         <v>188</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -14793,7 +14793,7 @@
         <v>189</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4">
         <v>1.0</v>
@@ -14806,13 +14806,13 @@
         <v>0.75</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>185</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -14820,7 +14820,7 @@
         <v>190</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C5" s="4">
         <v>0.97</v>
@@ -14836,10 +14836,10 @@
         <v>191</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -14847,7 +14847,7 @@
         <v>192</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C6" s="5">
         <v>0.95</v>
@@ -14863,45 +14863,45 @@
         <v>191</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C7" s="5">
         <v>0.71</v>
       </c>
-      <c r="D7" s="4">
-        <v>0.2</v>
+      <c r="D7" s="5">
+        <v>0.0</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="1"/>
-        <v>0.455</v>
+        <v>0.355</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C8" s="4">
         <v>0.15</v>
@@ -14914,21 +14914,21 @@
         <v>0.075</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C9" s="4">
         <v>0.15</v>
@@ -14941,21 +14941,21 @@
         <v>0.075</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C10" s="4">
         <v>0.0</v>
@@ -14968,21 +14968,21 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C11" s="4">
         <v>0.0</v>
@@ -14995,21 +14995,21 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C12" s="4">
         <v>0.0</v>
@@ -15022,21 +15022,21 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C13" s="4">
         <v>0.0</v>
@@ -15049,21 +15049,21 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C14" s="4">
         <v>0.0</v>
@@ -15076,21 +15076,21 @@
         <v>0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C15" s="4">
         <v>0.0</v>
@@ -15103,21 +15103,21 @@
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C16" s="4">
         <v>0.0</v>
@@ -15130,21 +15130,21 @@
         <v>0</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C17" s="4">
         <v>0.0</v>
@@ -15157,21 +15157,21 @@
         <v>0</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C18" s="4">
         <v>0.0</v>
@@ -15184,21 +15184,21 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C19" s="4">
         <v>0.0</v>
@@ -15211,21 +15211,21 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C20" s="4">
         <v>0.0</v>
@@ -15238,13 +15238,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1"/>
@@ -16252,51 +16252,51 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -16336,7 +16336,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -16376,7 +16376,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -16416,7 +16416,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -16456,7 +16456,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
